--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_19/design_variables_statistics.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_19/design_variables_statistics.xlsx
@@ -495,31 +495,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>69.02</v>
+        <v>69.63</v>
       </c>
       <c r="D2" t="n">
-        <v>16.95</v>
+        <v>15.91</v>
       </c>
       <c r="E2" t="n">
-        <v>24.56</v>
+        <v>22.85</v>
       </c>
       <c r="F2" t="n">
-        <v>47.3</v>
+        <v>49.24</v>
       </c>
       <c r="G2" t="n">
-        <v>53.99</v>
+        <v>56.58</v>
       </c>
       <c r="H2" t="n">
-        <v>64.95999999999999</v>
+        <v>65.34</v>
       </c>
       <c r="I2" t="n">
-        <v>84.20999999999999</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>52.7</v>
+        <v>50.76</v>
       </c>
     </row>
     <row r="3">
@@ -532,31 +532,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>48.65</v>
+        <v>45.55</v>
       </c>
       <c r="D3" t="n">
-        <v>0.59</v>
+        <v>0.66</v>
       </c>
       <c r="E3" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="F3" t="n">
-        <v>45.66</v>
+        <v>42.47</v>
       </c>
       <c r="G3" t="n">
-        <v>48.78</v>
+        <v>45.43</v>
       </c>
       <c r="H3" t="n">
-        <v>48.79</v>
+        <v>45.43</v>
       </c>
       <c r="I3" t="n">
-        <v>48.8</v>
+        <v>45.5</v>
       </c>
       <c r="J3" t="n">
-        <v>49.78</v>
+        <v>48.16</v>
       </c>
       <c r="K3" t="n">
-        <v>4.12</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="4">
@@ -569,31 +569,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>8.76</v>
+        <v>9.25</v>
       </c>
       <c r="D4" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="E4" t="n">
-        <v>16.76</v>
+        <v>13.81</v>
       </c>
       <c r="F4" t="n">
-        <v>5.46</v>
+        <v>6.27</v>
       </c>
       <c r="G4" t="n">
-        <v>7.59</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>9.08</v>
+        <v>9.57</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>10.14</v>
       </c>
       <c r="J4" t="n">
-        <v>10.48</v>
+        <v>10.66</v>
       </c>
       <c r="K4" t="n">
-        <v>5.02</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="5">
@@ -606,31 +606,31 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>148.81</v>
+        <v>118.56</v>
       </c>
       <c r="D5" t="n">
-        <v>20.97</v>
+        <v>16.46</v>
       </c>
       <c r="E5" t="n">
-        <v>14.09</v>
+        <v>13.88</v>
       </c>
       <c r="F5" t="n">
-        <v>122.32</v>
+        <v>93.23</v>
       </c>
       <c r="G5" t="n">
-        <v>131.79</v>
+        <v>110.13</v>
       </c>
       <c r="H5" t="n">
-        <v>138.78</v>
+        <v>117.63</v>
       </c>
       <c r="I5" t="n">
-        <v>166.75</v>
+        <v>122.06</v>
       </c>
       <c r="J5" t="n">
-        <v>184.66</v>
+        <v>160.49</v>
       </c>
       <c r="K5" t="n">
-        <v>62.35</v>
+        <v>67.26000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>3.42</v>
+        <v>2.53</v>
       </c>
       <c r="D6" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="E6" t="n">
-        <v>16.83</v>
+        <v>25.86</v>
       </c>
       <c r="F6" t="n">
-        <v>2.36</v>
+        <v>2.01</v>
       </c>
       <c r="G6" t="n">
-        <v>3.16</v>
+        <v>2.13</v>
       </c>
       <c r="H6" t="n">
-        <v>3.35</v>
+        <v>2.44</v>
       </c>
       <c r="I6" t="n">
-        <v>3.81</v>
+        <v>2.51</v>
       </c>
       <c r="J6" t="n">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="K6" t="n">
-        <v>2.19</v>
+        <v>2.51</v>
       </c>
     </row>
   </sheetData>
